--- a/output/pdf_financials_xlsx/FAN.xlsx
+++ b/output/pdf_financials_xlsx/FAN.xlsx
@@ -1177,10 +1177,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.143521</v>
+        <v>-0.143521</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.191716</v>
+        <v>-0.191716</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-0.332131</v>
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.143521</v>
+        <v>-0.143521</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.191716</v>
+        <v>-0.191716</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-0.332131</v>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.143521</v>
+        <v>-0.143521</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.191716</v>
+        <v>-0.191716</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-0.332131</v>
@@ -1761,10 +1761,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-4.784033</v>
+        <v>4.784033</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-6.390533</v>
+        <v>6.390533</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>8.303274999999999</v>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.143521</v>
+        <v>-0.143521</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.191716</v>
+        <v>-0.191716</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.332131</v>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.143521</v>
+        <v>-0.143521</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.191716</v>
+        <v>-0.191716</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.332131</v>
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -48373,13 +48373,13 @@
         </is>
       </c>
       <c r="E454" s="5" t="n">
-        <v>0.143521</v>
+        <v>-0.143521</v>
       </c>
       <c r="F454" s="5" t="n">
-        <v>0.191716</v>
+        <v>-0.191716</v>
       </c>
       <c r="G454" s="5" t="n">
-        <v>0.332131</v>
+        <v>-0.332131</v>
       </c>
       <c r="H454" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/FAN.xlsx
+++ b/output/pdf_financials_xlsx/FAN.xlsx
@@ -904,10 +904,10 @@
         <v>0.382093</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>1.213828</v>
+        <v>2.627249</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>1.887392</v>
+        <v>3.076105</v>
       </c>
     </row>
     <row r="11">
@@ -959,7 +959,7 @@
         <v>-2.627249</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-1.887392</v>
+        <v>-3.076105</v>
       </c>
     </row>
     <row r="12">
@@ -984,22 +984,22 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000393</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>3.3e-05</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>3.3e-05</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>5.4e-05</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>6e-05</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>1.6e-05</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
@@ -1008,7 +1008,7 @@
         <v>0</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.015486</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0</v>
@@ -1832,22 +1832,22 @@
         <v>-0.442098</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.038027</v>
+        <v>-0.03842</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.162916</v>
+        <v>-0.162949</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.198269</v>
+        <v>-0.198302</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.273176</v>
+        <v>-0.27323</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.587155</v>
+        <v>-0.587215</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.335499</v>
+        <v>-0.335515</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-2.426149</v>
@@ -1856,7 +1856,7 @@
         <v>-0.9194099999999999</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-1.849152</v>
+        <v>-1.864638</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>-2.400589</v>
@@ -1936,22 +1936,22 @@
         <v>-0.442098</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.038027</v>
+        <v>-0.03842</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.162916</v>
+        <v>-0.162949</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.198269</v>
+        <v>-0.198302</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.273176</v>
+        <v>-0.27323</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.587155</v>
+        <v>-0.587215</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.335499</v>
+        <v>-0.335515</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-2.406907</v>
@@ -1960,7 +1960,7 @@
         <v>-0.898419</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.82862</v>
+        <v>-1.844106</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>-2.373828</v>
@@ -2196,7 +2196,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.081497</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.00397</v>
@@ -2214,31 +2214,31 @@
         <v>0.11493</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.031662</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.05131</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.239383</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.276004</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.268108</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.813304</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.889581</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.13809</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>3.790374</v>
       </c>
     </row>
     <row r="35">
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.081497</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.00397</v>
@@ -2318,31 +2318,31 @@
         <v>0.11493</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.031662</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.05131</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.239383</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.276004</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.268108</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.813304</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.889581</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.13809</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>3.790374</v>
       </c>
     </row>
     <row r="37">
@@ -2924,7 +2924,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.081497</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0</v>
@@ -2942,31 +2942,31 @@
         <v>0.0025</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.040162</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.05381</v>
+        <v>0.0025</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.306883</v>
+        <v>0.0675</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.278521</v>
+        <v>0.002517</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.392691</v>
+        <v>0.124583</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.821971</v>
+        <v>0.008666999999999999</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.896581</v>
+        <v>0.007</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.437838</v>
+        <v>0.299748</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>4.015829</v>
+        <v>0.225455</v>
       </c>
     </row>
     <row r="49">
@@ -7012,16 +7012,16 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.022</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.024</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.024</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.031245</v>
       </c>
     </row>
     <row r="125">
@@ -7064,16 +7064,16 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.022</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.024</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.024</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.031245</v>
       </c>
     </row>
     <row r="126">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -9777,7 +9777,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11535,7 +11535,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
@@ -19944,7 +19944,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -22262,7 +22266,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
@@ -32427,7 +32435,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -33085,7 +33093,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -33154,10 +33162,10 @@
         </is>
       </c>
       <c r="R284" s="5" t="n">
-        <v>-2.627249</v>
+        <v>2.627249</v>
       </c>
       <c r="S284" s="5" t="n">
-        <v>-3.076105</v>
+        <v>3.076105</v>
       </c>
     </row>
     <row r="285">
@@ -33178,7 +33186,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -34537,7 +34545,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -34877,7 +34885,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -39007,7 +39015,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -39197,7 +39205,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -39743,7 +39751,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">

--- a/output/pdf_financials_xlsx/FAN.xlsx
+++ b/output/pdf_financials_xlsx/FAN.xlsx
@@ -3851,16 +3851,16 @@
         <v>0</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>0.543512</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>0.403064</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>0.817619</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>0.545334</v>
       </c>
     </row>
     <row r="65">
@@ -4007,16 +4007,16 @@
         <v>0</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.04725</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.079342</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.029</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.031994</v>
       </c>
     </row>
     <row r="68">
@@ -27262,7 +27262,11 @@
           <t>Shares issued for private placement</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -30241,7 +30245,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E252" s="5" t="n">
         <v>0.235</v>
       </c>
